--- a/Team-Data/2010-11/4-9-2010-11.xlsx
+++ b/Team-Data/2010-11/4-9-2010-11.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -664,61 +731,61 @@
         <v>79</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>0.544</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J2" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L2" t="n">
         <v>6.2</v>
       </c>
       <c r="M2" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="N2" t="n">
         <v>0.352</v>
       </c>
       <c r="O2" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P2" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="R2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T2" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="U2" t="n">
         <v>22</v>
       </c>
       <c r="V2" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X2" t="n">
         <v>4.1</v>
@@ -730,16 +797,16 @@
         <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>94.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.8</v>
+        <v>-0.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>13</v>
@@ -760,16 +827,16 @@
         <v>25</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AL2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AM2" t="n">
         <v>16</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>29</v>
@@ -784,22 +851,22 @@
         <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>27</v>
       </c>
       <c r="AU2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW2" t="n">
         <v>29</v>
       </c>
       <c r="AX2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY2" t="n">
         <v>5</v>
@@ -808,13 +875,13 @@
         <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BC2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -843,52 +910,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>0.701</v>
+        <v>0.696</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J3" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="K3" t="n">
         <v>0.487</v>
       </c>
       <c r="L3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>13.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O3" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P3" t="n">
         <v>23.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
         <v>7.8</v>
       </c>
       <c r="S3" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T3" t="n">
         <v>38.8</v>
@@ -897,7 +964,7 @@
         <v>23.6</v>
       </c>
       <c r="V3" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W3" t="n">
         <v>8.199999999999999</v>
@@ -906,7 +973,7 @@
         <v>4.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z3" t="n">
         <v>20.4</v>
@@ -915,13 +982,13 @@
         <v>20.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -951,31 +1018,31 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
@@ -984,7 +1051,7 @@
         <v>27</v>
       </c>
       <c r="AY3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
         <v>14</v>
@@ -993,7 +1060,7 @@
         <v>22</v>
       </c>
       <c r="BB3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC3" t="n">
         <v>5</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" t="n">
         <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>0.41</v>
+        <v>0.405</v>
       </c>
       <c r="H4" t="n">
         <v>48.3</v>
@@ -1046,7 +1113,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L4" t="n">
         <v>4.8</v>
@@ -1061,16 +1128,16 @@
         <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R4" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S4" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T4" t="n">
         <v>40.5</v>
@@ -1079,10 +1146,10 @@
         <v>20.8</v>
       </c>
       <c r="V4" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W4" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X4" t="n">
         <v>5.3</v>
@@ -1091,28 +1158,28 @@
         <v>6.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4</v>
+        <v>-4.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>16</v>
@@ -1136,22 +1203,22 @@
         <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT4" t="n">
         <v>21</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>19</v>
       </c>
       <c r="AU4" t="n">
         <v>20</v>
@@ -1169,10 +1236,10 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -1207,46 +1274,46 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E5" t="n">
         <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>0.756</v>
+        <v>0.747</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J5" t="n">
-        <v>80.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L5" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="O5" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
         <v>24.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.74</v>
+        <v>0.738</v>
       </c>
       <c r="R5" t="n">
         <v>11.8</v>
@@ -1255,7 +1322,7 @@
         <v>32.3</v>
       </c>
       <c r="T5" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U5" t="n">
         <v>22.3</v>
@@ -1273,25 +1340,25 @@
         <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
         <v>2</v>
@@ -1300,40 +1367,40 @@
         <v>11</v>
       </c>
       <c r="AI5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>19</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>21</v>
-      </c>
       <c r="AK5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
         <v>17</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP5" t="n">
         <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR5" t="n">
         <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="n">
         <v>9</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -1392,13 +1459,13 @@
         <v>79</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>0.203</v>
+        <v>0.215</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
@@ -1407,10 +1474,10 @@
         <v>35.1</v>
       </c>
       <c r="J6" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L6" t="n">
         <v>6.2</v>
@@ -1419,7 +1486,7 @@
         <v>18.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O6" t="n">
         <v>18.7</v>
@@ -1440,7 +1507,7 @@
         <v>40.4</v>
       </c>
       <c r="U6" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="n">
         <v>14.3</v>
@@ -1449,37 +1516,37 @@
         <v>6.7</v>
       </c>
       <c r="X6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
         <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>95.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
         <v>28</v>
@@ -1491,25 +1558,25 @@
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM6" t="n">
         <v>14</v>
       </c>
       <c r="AN6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP6" t="n">
         <v>9</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>7</v>
       </c>
       <c r="AQ6" t="n">
         <v>25</v>
       </c>
       <c r="AR6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS6" t="n">
         <v>23</v>
@@ -1518,13 +1585,13 @@
         <v>22</v>
       </c>
       <c r="AU6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV6" t="n">
         <v>19</v>
       </c>
-      <c r="AV6" t="n">
-        <v>21</v>
-      </c>
       <c r="AW6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX6" t="n">
         <v>28</v>
@@ -1533,13 +1600,13 @@
         <v>27</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
         <v>12</v>
       </c>
       <c r="BB6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -1571,43 +1638,43 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
         <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.679</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J7" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M7" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O7" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P7" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0.774</v>
@@ -1622,13 +1689,13 @@
         <v>41.2</v>
       </c>
       <c r="U7" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V7" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W7" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X7" t="n">
         <v>4.3</v>
@@ -1646,10 +1713,10 @@
         <v>99.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>6</v>
@@ -1664,13 +1731,13 @@
         <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL7" t="n">
         <v>8</v>
@@ -1682,7 +1749,7 @@
         <v>11</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
         <v>26</v>
@@ -1697,19 +1764,19 @@
         <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
         <v>23</v>
       </c>
       <c r="AX7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY7" t="n">
         <v>2</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -1768,46 +1835,46 @@
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J8" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L8" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.39</v>
+        <v>0.387</v>
       </c>
       <c r="O8" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="P8" t="n">
         <v>29.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.765</v>
+        <v>0.769</v>
       </c>
       <c r="R8" t="n">
         <v>9.6</v>
       </c>
       <c r="S8" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T8" t="n">
         <v>41.9</v>
       </c>
       <c r="U8" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="V8" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W8" t="n">
         <v>7.4</v>
@@ -1819,19 +1886,19 @@
         <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA8" t="n">
         <v>22.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.1</v>
+        <v>106.9</v>
       </c>
       <c r="AC8" t="n">
         <v>4.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1846,13 +1913,13 @@
         <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL8" t="n">
         <v>7</v>
@@ -1870,25 +1937,25 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>12</v>
       </c>
       <c r="AU8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV8" t="n">
         <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX8" t="n">
         <v>25</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E9" t="n">
         <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>0.359</v>
+        <v>0.354</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1965,19 +2032,19 @@
         <v>15.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="O9" t="n">
         <v>16.6</v>
       </c>
       <c r="P9" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.74</v>
+        <v>0.736</v>
       </c>
       <c r="R9" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S9" t="n">
         <v>27.1</v>
@@ -1989,22 +2056,22 @@
         <v>20.9</v>
       </c>
       <c r="V9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
         <v>7.3</v>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z9" t="n">
         <v>19.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB9" t="n">
         <v>96.59999999999999</v>
@@ -2013,7 +2080,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
@@ -2028,13 +2095,13 @@
         <v>6</v>
       </c>
       <c r="AI9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ9" t="n">
         <v>13</v>
       </c>
       <c r="AK9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
         <v>20</v>
@@ -2049,10 +2116,10 @@
         <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR9" t="n">
         <v>12</v>
@@ -2067,7 +2134,7 @@
         <v>18</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
         <v>16</v>
@@ -2085,7 +2152,7 @@
         <v>28</v>
       </c>
       <c r="BB9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC9" t="n">
         <v>23</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
         <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>0.436</v>
+        <v>0.443</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="J10" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.46</v>
+        <v>0.462</v>
       </c>
       <c r="L10" t="n">
         <v>8.300000000000001</v>
@@ -2150,13 +2217,13 @@
         <v>0.391</v>
       </c>
       <c r="O10" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P10" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R10" t="n">
         <v>11.6</v>
@@ -2165,16 +2232,16 @@
         <v>28.9</v>
       </c>
       <c r="T10" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U10" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V10" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W10" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X10" t="n">
         <v>4.9</v>
@@ -2183,19 +2250,19 @@
         <v>4.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
         <v>18.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>102.8</v>
+        <v>103.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AL10" t="n">
         <v>5</v>
@@ -2237,10 +2304,10 @@
         <v>18</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT10" t="n">
         <v>20</v>
@@ -2249,22 +2316,22 @@
         <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW10" t="n">
         <v>2</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ10" t="n">
         <v>23</v>
       </c>
       <c r="BA10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB10" t="n">
         <v>7</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -2299,55 +2366,55 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>0.538</v>
+        <v>0.519</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J11" t="n">
-        <v>84.8</v>
+        <v>85</v>
       </c>
       <c r="K11" t="n">
         <v>0.455</v>
       </c>
       <c r="L11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="P11" t="n">
-        <v>25.1</v>
+        <v>25.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.799</v>
+        <v>0.802</v>
       </c>
       <c r="R11" t="n">
         <v>11.6</v>
       </c>
       <c r="S11" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="T11" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U11" t="n">
         <v>23.7</v>
@@ -2359,31 +2426,31 @@
         <v>7.1</v>
       </c>
       <c r="X11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y11" t="n">
         <v>5.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>105.6</v>
+        <v>106</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
         <v>14</v>
@@ -2395,7 +2462,7 @@
         <v>4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK11" t="n">
         <v>21</v>
@@ -2407,22 +2474,22 @@
         <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO11" t="n">
         <v>5</v>
       </c>
       <c r="AP11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT11" t="n">
         <v>8</v>
@@ -2434,19 +2501,19 @@
         <v>6</v>
       </c>
       <c r="AW11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY11" t="n">
         <v>21</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>22</v>
       </c>
       <c r="AZ11" t="n">
         <v>9</v>
       </c>
       <c r="BA11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" t="n">
         <v>37</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>0.468</v>
+        <v>0.463</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,10 +2566,10 @@
         <v>36.7</v>
       </c>
       <c r="J12" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L12" t="n">
         <v>7.1</v>
@@ -2511,7 +2578,7 @@
         <v>20.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O12" t="n">
         <v>19.4</v>
@@ -2520,22 +2587,22 @@
         <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U12" t="n">
         <v>19.7</v>
       </c>
       <c r="V12" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W12" t="n">
         <v>7.1</v>
@@ -2547,22 +2614,22 @@
         <v>5.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA12" t="n">
         <v>21.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF12" t="n">
         <v>19</v>
@@ -2571,16 +2638,16 @@
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>10</v>
@@ -2592,7 +2659,7 @@
         <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP12" t="n">
         <v>10</v>
@@ -2607,13 +2674,13 @@
         <v>3</v>
       </c>
       <c r="AT12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
         <v>28</v>
       </c>
       <c r="AV12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW12" t="n">
         <v>19</v>
@@ -2628,13 +2695,13 @@
         <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
         <v>11</v>
       </c>
       <c r="BC12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -2681,10 +2748,10 @@
         <v>36.7</v>
       </c>
       <c r="J13" t="n">
-        <v>80.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L13" t="n">
         <v>6.3</v>
@@ -2693,13 +2760,13 @@
         <v>18.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O13" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P13" t="n">
-        <v>26.6</v>
+        <v>26.9</v>
       </c>
       <c r="Q13" t="n">
         <v>0.708</v>
@@ -2723,7 +2790,7 @@
         <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y13" t="n">
         <v>4.9</v>
@@ -2735,10 +2802,10 @@
         <v>22.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>-3.2</v>
+        <v>-3</v>
       </c>
       <c r="AD13" t="n">
         <v>1</v>
@@ -2759,10 +2826,10 @@
         <v>21</v>
       </c>
       <c r="AJ13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL13" t="n">
         <v>13</v>
@@ -2771,7 +2838,7 @@
         <v>11</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO13" t="n">
         <v>8</v>
@@ -2783,7 +2850,7 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS13" t="n">
         <v>15</v>
@@ -2792,7 +2859,7 @@
         <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV13" t="n">
         <v>29</v>
@@ -2801,7 +2868,7 @@
         <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY13" t="n">
         <v>18</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
         <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.696</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,10 +2930,10 @@
         <v>38.1</v>
       </c>
       <c r="J14" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L14" t="n">
         <v>6.4</v>
@@ -2875,22 +2942,22 @@
         <v>18.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O14" t="n">
         <v>18.6</v>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.774</v>
+        <v>0.775</v>
       </c>
       <c r="R14" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S14" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
         <v>44.1</v>
@@ -2902,7 +2969,7 @@
         <v>13.2</v>
       </c>
       <c r="W14" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X14" t="n">
         <v>5.2</v>
@@ -2911,28 +2978,28 @@
         <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.1</v>
+        <v>101.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
         <v>16</v>
@@ -2944,7 +3011,7 @@
         <v>12</v>
       </c>
       <c r="AK14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL14" t="n">
         <v>12</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>11</v>
@@ -2971,7 +3038,7 @@
         <v>6</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU14" t="n">
         <v>14</v>
@@ -2980,16 +3047,16 @@
         <v>5</v>
       </c>
       <c r="AW14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
         <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA14" t="n">
         <v>17</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
         <v>45</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>0.577</v>
+        <v>0.57</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
@@ -3045,7 +3112,7 @@
         <v>39.1</v>
       </c>
       <c r="J15" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K15" t="n">
         <v>0.47</v>
@@ -3054,13 +3121,13 @@
         <v>3.7</v>
       </c>
       <c r="M15" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="O15" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P15" t="n">
         <v>24.1</v>
@@ -3069,16 +3136,16 @@
         <v>0.75</v>
       </c>
       <c r="R15" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S15" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T15" t="n">
         <v>41</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>13.8</v>
@@ -3087,10 +3154,10 @@
         <v>9.5</v>
       </c>
       <c r="X15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z15" t="n">
         <v>20.7</v>
@@ -3099,22 +3166,22 @@
         <v>21.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
         <v>6</v>
@@ -3138,7 +3205,7 @@
         <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP15" t="n">
         <v>15</v>
@@ -3147,7 +3214,7 @@
         <v>23</v>
       </c>
       <c r="AR15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
         <v>24</v>
@@ -3156,7 +3223,7 @@
         <v>17</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
         <v>12</v>
@@ -3168,13 +3235,13 @@
         <v>7</v>
       </c>
       <c r="AY15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ15" t="n">
         <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>0.701</v>
+        <v>0.696</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J16" t="n">
-        <v>77.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.482</v>
+        <v>0.481</v>
       </c>
       <c r="L16" t="n">
         <v>6.6</v>
@@ -3239,7 +3306,7 @@
         <v>17.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O16" t="n">
         <v>21.7</v>
@@ -3248,22 +3315,22 @@
         <v>28.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R16" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S16" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T16" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U16" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V16" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W16" t="n">
         <v>6.6</v>
@@ -3272,22 +3339,22 @@
         <v>5.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
         <v>20.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>102.6</v>
+        <v>102.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3302,7 +3369,7 @@
         <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
@@ -3317,7 +3384,7 @@
         <v>15</v>
       </c>
       <c r="AN16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO16" t="n">
         <v>3</v>
@@ -3326,7 +3393,7 @@
         <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR16" t="n">
         <v>27</v>
@@ -3338,13 +3405,13 @@
         <v>9</v>
       </c>
       <c r="AU16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV16" t="n">
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX16" t="n">
         <v>8</v>
@@ -3353,10 +3420,10 @@
         <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -3394,25 +3461,25 @@
         <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>0.418</v>
+        <v>0.405</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="J17" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.43</v>
+        <v>0.429</v>
       </c>
       <c r="L17" t="n">
         <v>5.9</v>
@@ -3421,55 +3488,55 @@
         <v>17.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O17" t="n">
         <v>17.2</v>
       </c>
       <c r="P17" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.756</v>
+        <v>0.753</v>
       </c>
       <c r="R17" t="n">
         <v>10.6</v>
       </c>
       <c r="S17" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T17" t="n">
-        <v>40.7</v>
+        <v>40.9</v>
       </c>
       <c r="U17" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="V17" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W17" t="n">
         <v>7.4</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y17" t="n">
         <v>4.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>91.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
@@ -3481,7 +3548,7 @@
         <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
         <v>30</v>
@@ -3505,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="AP17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ17" t="n">
         <v>22</v>
@@ -3526,19 +3593,19 @@
         <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY17" t="n">
         <v>16</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -3600,28 +3667,28 @@
         <v>7.2</v>
       </c>
       <c r="M18" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>0.375</v>
+        <v>0.377</v>
       </c>
       <c r="O18" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P18" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R18" t="n">
         <v>13.3</v>
       </c>
       <c r="S18" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T18" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U18" t="n">
         <v>20.1</v>
@@ -3636,22 +3703,22 @@
         <v>5.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB18" t="n">
-        <v>100.5</v>
+        <v>100.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.5</v>
+        <v>-6.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3663,16 +3730,16 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>2</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
         <v>9</v>
@@ -3690,7 +3757,7 @@
         <v>14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR18" t="n">
         <v>1</v>
@@ -3711,10 +3778,10 @@
         <v>18</v>
       </c>
       <c r="AX18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ18" t="n">
         <v>27</v>
@@ -3726,7 +3793,7 @@
         <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
         <v>55</v>
       </c>
       <c r="G19" t="n">
-        <v>0.295</v>
+        <v>0.304</v>
       </c>
       <c r="H19" t="n">
         <v>48.8</v>
@@ -3776,16 +3843,16 @@
         <v>80.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L19" t="n">
         <v>5.7</v>
       </c>
       <c r="M19" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O19" t="n">
         <v>17.4</v>
@@ -3794,13 +3861,13 @@
         <v>23.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R19" t="n">
         <v>11.1</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T19" t="n">
         <v>41.2</v>
@@ -3818,22 +3885,22 @@
         <v>4.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA19" t="n">
         <v>20</v>
       </c>
       <c r="AB19" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.4</v>
+        <v>-6.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>25</v>
@@ -3854,7 +3921,7 @@
         <v>15</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
         <v>21</v>
@@ -3863,13 +3930,13 @@
         <v>20</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO19" t="n">
         <v>25</v>
       </c>
       <c r="AP19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ19" t="n">
         <v>21</v>
@@ -3878,16 +3945,16 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU19" t="n">
         <v>17</v>
       </c>
       <c r="AV19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW19" t="n">
         <v>30</v>
@@ -3896,10 +3963,10 @@
         <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA19" t="n">
         <v>25</v>
@@ -3908,7 +3975,7 @@
         <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F20" t="n">
         <v>33</v>
       </c>
       <c r="G20" t="n">
-        <v>0.577</v>
+        <v>0.582</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3964,28 +4031,28 @@
         <v>5.4</v>
       </c>
       <c r="M20" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O20" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="R20" t="n">
         <v>10.1</v>
       </c>
       <c r="S20" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T20" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U20" t="n">
         <v>20.6</v>
@@ -4000,43 +4067,43 @@
         <v>4.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB20" t="n">
         <v>95.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE20" t="n">
         <v>11</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>10</v>
       </c>
       <c r="AF20" t="n">
         <v>10</v>
       </c>
       <c r="AG20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
         <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
         <v>22</v>
@@ -4048,7 +4115,7 @@
         <v>14</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
@@ -4057,16 +4124,16 @@
         <v>14</v>
       </c>
       <c r="AR20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT20" t="n">
         <v>23</v>
       </c>
-      <c r="AS20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>24</v>
-      </c>
       <c r="AU20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4087,10 +4154,10 @@
         <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E21" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F21" t="n">
         <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>0.513</v>
+        <v>0.519</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4137,40 +4204,40 @@
         <v>38.4</v>
       </c>
       <c r="J21" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="K21" t="n">
         <v>0.459</v>
       </c>
       <c r="L21" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M21" t="n">
         <v>25.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O21" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="P21" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R21" t="n">
         <v>10.4</v>
       </c>
       <c r="S21" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T21" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U21" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V21" t="n">
         <v>13.7</v>
@@ -4179,7 +4246,7 @@
         <v>7.6</v>
       </c>
       <c r="X21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y21" t="n">
         <v>4.4</v>
@@ -4188,28 +4255,28 @@
         <v>21.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>106.8</v>
+        <v>106.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4221,7 +4288,7 @@
         <v>18</v>
       </c>
       <c r="AL21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM21" t="n">
         <v>2</v>
@@ -4233,19 +4300,19 @@
         <v>4</v>
       </c>
       <c r="AP21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ21" t="n">
         <v>2</v>
       </c>
       <c r="AR21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
         <v>20</v>
       </c>
       <c r="AT21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU21" t="n">
         <v>15</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -4301,43 +4368,43 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F22" t="n">
         <v>26</v>
       </c>
       <c r="G22" t="n">
-        <v>0.667</v>
+        <v>0.671</v>
       </c>
       <c r="H22" t="n">
         <v>48.8</v>
       </c>
       <c r="I22" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J22" t="n">
         <v>80.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M22" t="n">
         <v>17.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O22" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="P22" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="Q22" t="n">
         <v>0.822</v>
@@ -4346,40 +4413,40 @@
         <v>11.1</v>
       </c>
       <c r="S22" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T22" t="n">
         <v>42.7</v>
       </c>
       <c r="U22" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V22" t="n">
         <v>13.9</v>
       </c>
       <c r="W22" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y22" t="n">
         <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB22" t="n">
         <v>104.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>7</v>
@@ -4391,22 +4458,22 @@
         <v>7</v>
       </c>
       <c r="AH22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AL22" t="n">
         <v>18</v>
       </c>
       <c r="AM22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN22" t="n">
         <v>19</v>
@@ -4442,10 +4509,10 @@
         <v>3</v>
       </c>
       <c r="AY22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="n">
         <v>29</v>
       </c>
       <c r="G23" t="n">
-        <v>0.628</v>
+        <v>0.633</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
       </c>
       <c r="I23" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J23" t="n">
         <v>78.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L23" t="n">
         <v>9.4</v>
@@ -4513,7 +4580,7 @@
         <v>25.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O23" t="n">
         <v>17.7</v>
@@ -4522,16 +4589,16 @@
         <v>25.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R23" t="n">
         <v>10.3</v>
       </c>
       <c r="S23" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T23" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U23" t="n">
         <v>19.9</v>
@@ -4552,16 +4619,16 @@
         <v>20.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB23" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>8</v>
@@ -4576,13 +4643,13 @@
         <v>11</v>
       </c>
       <c r="AI23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4594,7 +4661,7 @@
         <v>10</v>
       </c>
       <c r="AO23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
         <v>5</v>
@@ -4612,13 +4679,13 @@
         <v>6</v>
       </c>
       <c r="AU23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW23" t="n">
         <v>27</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>26</v>
       </c>
       <c r="AX23" t="n">
         <v>16</v>
@@ -4633,7 +4700,7 @@
         <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC23" t="n">
         <v>6</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -4665,22 +4732,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E24" t="n">
         <v>41</v>
       </c>
       <c r="F24" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
-        <v>0.519</v>
+        <v>0.513</v>
       </c>
       <c r="H24" t="n">
         <v>48.6</v>
       </c>
       <c r="I24" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J24" t="n">
         <v>82.5</v>
@@ -4698,10 +4765,10 @@
         <v>0.356</v>
       </c>
       <c r="O24" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P24" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q24" t="n">
         <v>0.769</v>
@@ -4716,13 +4783,13 @@
         <v>42</v>
       </c>
       <c r="U24" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V24" t="n">
         <v>13</v>
       </c>
       <c r="W24" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X24" t="n">
         <v>4.3</v>
@@ -4731,40 +4798,40 @@
         <v>4.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA24" t="n">
         <v>18.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH24" t="n">
         <v>4</v>
       </c>
       <c r="AI24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ24" t="n">
         <v>11</v>
       </c>
       <c r="AK24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL24" t="n">
         <v>23</v>
@@ -4779,13 +4846,13 @@
         <v>23</v>
       </c>
       <c r="AP24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ24" t="n">
         <v>12</v>
       </c>
       <c r="AR24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
         <v>10</v>
@@ -4797,13 +4864,13 @@
         <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW24" t="n">
         <v>10</v>
       </c>
       <c r="AX24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY24" t="n">
         <v>13</v>
@@ -4815,10 +4882,10 @@
         <v>27</v>
       </c>
       <c r="BB24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -4847,13 +4914,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G25" t="n">
         <v>0.481</v>
@@ -4862,10 +4929,10 @@
         <v>48.8</v>
       </c>
       <c r="I25" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="J25" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K25" t="n">
         <v>0.471</v>
@@ -4877,31 +4944,31 @@
         <v>22.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O25" t="n">
         <v>17.9</v>
       </c>
       <c r="P25" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="R25" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S25" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T25" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U25" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V25" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W25" t="n">
         <v>6.7</v>
@@ -4913,19 +4980,19 @@
         <v>4.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.9</v>
+        <v>104.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>17</v>
@@ -4958,7 +5025,7 @@
         <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP25" t="n">
         <v>20</v>
@@ -4976,13 +5043,13 @@
         <v>23</v>
       </c>
       <c r="AU25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX25" t="n">
         <v>21</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E26" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F26" t="n">
         <v>33</v>
       </c>
       <c r="G26" t="n">
-        <v>0.577</v>
+        <v>0.588</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>80.2</v>
+        <v>80.5</v>
       </c>
       <c r="K26" t="n">
         <v>0.449</v>
@@ -5059,34 +5126,34 @@
         <v>18.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.338</v>
+        <v>0.341</v>
       </c>
       <c r="O26" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P26" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.805</v>
+        <v>0.804</v>
       </c>
       <c r="R26" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S26" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="T26" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="U26" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V26" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W26" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X26" t="n">
         <v>4.4</v>
@@ -5098,16 +5165,16 @@
         <v>19.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>10</v>
@@ -5119,37 +5186,37 @@
         <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
         <v>23</v>
       </c>
       <c r="AL26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AM26" t="n">
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS26" t="n">
         <v>29</v>
@@ -5161,7 +5228,7 @@
         <v>16</v>
       </c>
       <c r="AV26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW26" t="n">
         <v>4</v>
@@ -5176,7 +5243,7 @@
         <v>5</v>
       </c>
       <c r="BA26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB26" t="n">
         <v>24</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F27" t="n">
         <v>56</v>
       </c>
       <c r="G27" t="n">
-        <v>0.282</v>
+        <v>0.291</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5244,16 +5311,16 @@
         <v>0.338</v>
       </c>
       <c r="O27" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="P27" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="Q27" t="n">
         <v>0.731</v>
       </c>
       <c r="R27" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S27" t="n">
         <v>30.7</v>
@@ -5268,7 +5335,7 @@
         <v>16.2</v>
       </c>
       <c r="W27" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X27" t="n">
         <v>4.8</v>
@@ -5280,16 +5347,16 @@
         <v>22</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC27" t="n">
         <v>-5.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5304,10 +5371,10 @@
         <v>11</v>
       </c>
       <c r="AI27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK27" t="n">
         <v>22</v>
@@ -5322,10 +5389,10 @@
         <v>26</v>
       </c>
       <c r="AO27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ27" t="n">
         <v>28</v>
@@ -5337,19 +5404,19 @@
         <v>14</v>
       </c>
       <c r="AT27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV27" t="n">
         <v>28</v>
       </c>
       <c r="AW27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -5411,10 +5478,10 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L28" t="n">
         <v>8.4</v>
@@ -5426,19 +5493,19 @@
         <v>0.399</v>
       </c>
       <c r="O28" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P28" t="n">
         <v>23.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.764</v>
+        <v>0.766</v>
       </c>
       <c r="R28" t="n">
         <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T28" t="n">
         <v>41.8</v>
@@ -5447,10 +5514,10 @@
         <v>22.4</v>
       </c>
       <c r="V28" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W28" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
         <v>4.6</v>
@@ -5465,13 +5532,13 @@
         <v>20.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.6</v>
+        <v>103.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,13 +5550,13 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
         <v>6</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
         <v>3</v>
@@ -5513,7 +5580,7 @@
         <v>16</v>
       </c>
       <c r="AR28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS28" t="n">
         <v>7</v>
@@ -5525,19 +5592,19 @@
         <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW28" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY28" t="n">
         <v>14</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA28" t="n">
         <v>19</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E29" t="n">
         <v>21</v>
       </c>
       <c r="F29" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G29" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5593,10 +5660,10 @@
         <v>38.6</v>
       </c>
       <c r="J29" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K29" t="n">
-        <v>0.468</v>
+        <v>0.466</v>
       </c>
       <c r="L29" t="n">
         <v>4.3</v>
@@ -5620,7 +5687,7 @@
         <v>11.6</v>
       </c>
       <c r="S29" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="T29" t="n">
         <v>40.2</v>
@@ -5629,7 +5696,7 @@
         <v>22.1</v>
       </c>
       <c r="V29" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W29" t="n">
         <v>7.1</v>
@@ -5638,40 +5705,40 @@
         <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="AC29" t="n">
         <v>-6.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF29" t="n">
         <v>27</v>
       </c>
       <c r="AG29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI29" t="n">
         <v>5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK29" t="n">
         <v>8</v>
@@ -5689,16 +5756,16 @@
         <v>16</v>
       </c>
       <c r="AP29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR29" t="n">
         <v>8</v>
       </c>
       <c r="AS29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT29" t="n">
         <v>25</v>
@@ -5710,25 +5777,25 @@
         <v>22</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX29" t="n">
         <v>26</v>
       </c>
       <c r="AY29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA29" t="n">
         <v>26</v>
       </c>
       <c r="BB29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E30" t="n">
         <v>37</v>
       </c>
       <c r="F30" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G30" t="n">
-        <v>0.474</v>
+        <v>0.468</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J30" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L30" t="n">
         <v>5.3</v>
@@ -5787,31 +5854,31 @@
         <v>15.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="O30" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="P30" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R30" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S30" t="n">
-        <v>28.4</v>
+        <v>28.6</v>
       </c>
       <c r="T30" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="U30" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V30" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W30" t="n">
         <v>7.7</v>
@@ -5823,22 +5890,22 @@
         <v>5.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>99.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1.6</v>
+        <v>-2</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
@@ -5850,13 +5917,13 @@
         <v>6</v>
       </c>
       <c r="AI30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ30" t="n">
         <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5865,13 +5932,13 @@
         <v>22</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
         <v>9</v>
@@ -5880,7 +5947,7 @@
         <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
         <v>26</v>
@@ -5889,7 +5956,7 @@
         <v>5</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
         <v>7</v>
@@ -5904,10 +5971,10 @@
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BB30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC30" t="n">
         <v>20</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
@@ -5942,34 +6009,34 @@
         <v>79</v>
       </c>
       <c r="E31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G31" t="n">
-        <v>0.278</v>
+        <v>0.266</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J31" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.444</v>
+        <v>0.442</v>
       </c>
       <c r="L31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M31" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.333</v>
+        <v>0.331</v>
       </c>
       <c r="O31" t="n">
         <v>18.1</v>
@@ -5981,46 +6048,46 @@
         <v>0.745</v>
       </c>
       <c r="R31" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S31" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="U31" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V31" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W31" t="n">
         <v>8</v>
       </c>
       <c r="X31" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y31" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA31" t="n">
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>97.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.2</v>
+        <v>-8</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF31" t="n">
         <v>27</v>
@@ -6032,13 +6099,13 @@
         <v>5</v>
       </c>
       <c r="AI31" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AJ31" t="n">
         <v>5</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>27</v>
@@ -6062,16 +6129,16 @@
         <v>3</v>
       </c>
       <c r="AS31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU31" t="n">
         <v>29</v>
       </c>
       <c r="AV31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
         <v>5</v>
@@ -6083,7 +6150,7 @@
         <v>19</v>
       </c>
       <c r="AZ31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-9-2010-11</t>
+          <t>2011-04-09</t>
         </is>
       </c>
     </row>
